--- a/Internship_artifacts/Mobashir_Ashraf_Unit_Test_Plan.xlsx
+++ b/Internship_artifacts/Mobashir_Ashraf_Unit_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jaz\Desktop\current\current\Internship_artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314F3625-DD5D-4C14-BB87-63BBEC8402C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABEE89E-F8F9-43FF-A09D-B99ABE1BA07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -622,9 +622,9 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" customWidth="1"/>
-    <col min="2" max="2" width="22.77734375" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="1" max="1" width="5.21875" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="58.33203125" customWidth="1"/>
     <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="53.77734375" customWidth="1"/>
     <col min="6" max="6" width="52.44140625" customWidth="1"/>
